--- a/output/pdf_financials_xlsx/ROAD.xlsx
+++ b/output/pdf_financials_xlsx/ROAD.xlsx
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.144992</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.261393</v>
       </c>
     </row>
     <row r="93">
@@ -2820,7 +2820,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>1.144992</v>
       </c>

--- a/output/pdf_financials_xlsx/ROAD.xlsx
+++ b/output/pdf_financials_xlsx/ROAD.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.041464</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003265</v>
       </c>
     </row>
     <row r="13">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.14052</v>
+        <v>-3.181984</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.804939</v>
+        <v>-1.808204</v>
       </c>
     </row>
     <row r="28">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.14052</v>
+        <v>-3.181984</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.804939</v>
+        <v>-1.808204</v>
       </c>
     </row>
     <row r="30">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.155457</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.050435</v>
       </c>
     </row>
     <row r="35">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.751792</v>
+        <v>0.907249</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.545897</v>
+        <v>2.596332</v>
       </c>
     </row>
     <row r="37">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.548783</v>
+        <v>0.393326</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.549652</v>
+        <v>0.499217</v>
       </c>
     </row>
     <row r="49">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">

--- a/output/pdf_financials_xlsx/ROAD.xlsx
+++ b/output/pdf_financials_xlsx/ROAD.xlsx
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.01881</v>
+        <v>0.022823</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.004034</v>
+        <v>-0.010123</v>
       </c>
     </row>
     <row r="102">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.032594</v>
+        <v>0.074227</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.429318</v>
+        <v>0.423229</v>
       </c>
     </row>
     <row r="107">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005919</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.433257</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-2.935177</v>
       </c>
     </row>
     <row r="115">
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.618695</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.96336</v>
       </c>
     </row>
     <row r="116">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005919</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.295496</v>
+        <v>-1.301415</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.40167</v>
@@ -3318,7 +3318,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.041633</v>
       </c>
@@ -3476,7 +3480,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>-0.005919</v>
       </c>
@@ -3502,7 +3510,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>-0.433257</v>
       </c>
@@ -3526,7 +3538,11 @@
           <t>Proceeds from sales of marketable securities</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.618695</v>
       </c>
